--- a/engine/chart2/qa/extras/data/xlsx/sunburst.xlsx
+++ b/engine/chart2/qa/extras/data/xlsx/sunburst.xlsx
@@ -168,6 +168,9 @@
             <cx:visibility seriesName="0" categoryName="1" value="0"/>
           </cx:dataLabels>
           <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:parentLabelLayout val="overlapping"/>
+          </cx:layoutPr>
         </cx:series>
       </cx:plotAreaRegion>
     </cx:plotArea>
